--- a/output/pdf_financials_xlsx/CMP.xlsx
+++ b/output/pdf_financials_xlsx/CMP.xlsx
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.043194</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.05546</v>
       </c>
     </row>
     <row r="93">
@@ -2582,7 +2582,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.043194</v>
       </c>

--- a/output/pdf_financials_xlsx/CMP.xlsx
+++ b/output/pdf_financials_xlsx/CMP.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>6.600000000000001e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001636</v>
       </c>
     </row>
     <row r="13">
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.079211</v>
+        <v>-0.079277</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.132044</v>
+        <v>-0.13368</v>
       </c>
     </row>
     <row r="28">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.079211</v>
+        <v>-0.079277</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.132044</v>
+        <v>-0.13368</v>
       </c>
     </row>
     <row r="30">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.102995</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.024322</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.102995</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.024322</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.106654</v>
+        <v>0.003659</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.028384</v>
+        <v>0.004062</v>
       </c>
     </row>
     <row r="49">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
